--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5435</v>
+        <v>7292</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8091</v>
+        <v>9974</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2656</v>
+        <v>-2682</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>15</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6165</v>
+        <v>10470</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8091</v>
+        <v>9974</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1926</v>
+        <v>496</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10156</v>
+        <v>10470</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8091</v>
+        <v>13696</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2065</v>
+        <v>-3226</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,40 +676,40 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6069</v>
+        <v>11242</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8737</v>
+        <v>13696</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2668</v>
+        <v>-2454</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10757</v>
+        <v>11835</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18582</v>
+        <v>13696</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-7825</v>
+        <v>-1861</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>-16</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15191</v>
+        <v>11835</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18582</v>
+        <v>13696</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3391</v>
+        <v>-1861</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15376</v>
+        <v>11918</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>18582</v>
+        <v>13696</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3206</v>
+        <v>-1778</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>16086</v>
+        <v>6603</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>18582</v>
+        <v>13696</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2496</v>
+        <v>-7093</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16965</v>
+        <v>8808</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>18582</v>
+        <v>13696</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1617</v>
+        <v>-4888</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18024</v>
+        <v>9891</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>18582</v>
+        <v>13696</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-558</v>
+        <v>-3805</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,26 +1001,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10118</v>
+        <v>9891</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-6525</v>
+        <v>-3805</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10574</v>
+        <v>10443</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6069</v>
+        <v>-3253</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>7</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10574</v>
+        <v>10443</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6069</v>
+        <v>-3253</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>7</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10865</v>
+        <v>10443</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5778</v>
+        <v>-3253</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11770</v>
+        <v>10443</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4873</v>
+        <v>-3253</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>7</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11834</v>
+        <v>10443</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4809</v>
+        <v>-3253</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12399</v>
+        <v>11146</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4244</v>
+        <v>-2550</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1292,9 +1292,9 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>29-MAR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14020</v>
+        <v>11835</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16643</v>
+        <v>13696</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2623</v>
+        <v>-1861</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14261</v>
+        <v>5638</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16643</v>
+        <v>8044</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2382</v>
+        <v>-2406</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>17315</v>
+        <v>6465</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16643</v>
+        <v>8044</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>672</v>
+        <v>-1579</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>14-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6575</v>
+        <v>9630</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5088</v>
+        <v>8044</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1487</v>
+        <v>1586</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>14-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6575</v>
+        <v>5913</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>5088</v>
+        <v>8044</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1487</v>
+        <v>-2131</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6575</v>
+        <v>5913</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5088</v>
+        <v>8044</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1487</v>
+        <v>-2131</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1576,36 +1576,36 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>05-APR-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6322</v>
+        <v>7672</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1234</v>
+        <v>1971</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,36 +1621,36 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>16-MAR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6322</v>
+        <v>7672</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1234</v>
+        <v>1971</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6575</v>
+        <v>7672</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1487</v>
+        <v>1971</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6322</v>
+        <v>7154</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1234</v>
+        <v>1453</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>40</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>12-APR-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6322</v>
+        <v>7154</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1234</v>
+        <v>1453</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>40</v>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>21-MAR-26</t>
+          <t>12-APR-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6575</v>
+        <v>7672</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1487</v>
+        <v>1971</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>21-MAR-26</t>
+          <t>14-APR-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6575</v>
+        <v>7672</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>5088</v>
+        <v>5701</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1487</v>
+        <v>1971</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,33 +1901,798 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>4948</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>6514</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1566</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>6514</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>19-APR-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>flyadeal F3-776</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
-        <v>5435</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>5480</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="D35" s="2" t="n">
+        <v>4121</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>6514</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-2393</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>19-APR-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>7154</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>6514</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>19-APR-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>6514</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>21-APR-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>7154</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>21-APR-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>23-APR-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>26-APR-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>7154</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>26-APR-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>28-APR-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>30-APR-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>7154</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>30-APR-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>7154</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>30-APR-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-675</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>30-APR-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-693</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>7672</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>5701</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7292</v>
+        <v>8327</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9974</v>
+        <v>7289</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2682</v>
+        <v>1038</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10470</v>
+        <v>8327</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9974</v>
+        <v>7289</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>496</v>
+        <v>1038</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10470</v>
+        <v>8327</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13696</v>
+        <v>7289</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3226</v>
+        <v>1038</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11242</v>
+        <v>8327</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13696</v>
+        <v>7289</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2454</v>
+        <v>1038</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11835</v>
+        <v>8565</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13696</v>
+        <v>7289</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1861</v>
+        <v>1276</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11835</v>
+        <v>8565</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13696</v>
+        <v>7289</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1861</v>
+        <v>1276</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>28-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11918</v>
+        <v>4615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1778</v>
+        <v>-2267</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6603</v>
+        <v>4615</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-7093</v>
+        <v>-2267</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>15</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8808</v>
+        <v>4615</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4888</v>
+        <v>-2267</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>15</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9891</v>
+        <v>4615</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3805</v>
+        <v>-2267</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9891</v>
+        <v>5317</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3805</v>
+        <v>-1565</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10443</v>
+        <v>5317</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3253</v>
+        <v>-1565</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10443</v>
+        <v>4615</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3253</v>
+        <v>-2267</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10443</v>
+        <v>4615</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3253</v>
+        <v>-2267</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10443</v>
+        <v>5317</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3253</v>
+        <v>-1565</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10443</v>
+        <v>5317</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3253</v>
+        <v>-1565</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11146</v>
+        <v>5317</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2550</v>
+        <v>-1565</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>29-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11835</v>
+        <v>5317</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13696</v>
+        <v>6882</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1861</v>
+        <v>-1565</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>19-APR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5638</v>
+        <v>7281</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8044</v>
+        <v>6068</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2406</v>
+        <v>1213</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>19-APR-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6465</v>
+        <v>7281</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8044</v>
+        <v>6068</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1579</v>
+        <v>1213</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>19-APR-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9630</v>
+        <v>7780</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>8044</v>
+        <v>6068</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1586</v>
+        <v>1712</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>19-APR-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5913</v>
+        <v>7780</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8044</v>
+        <v>6068</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2131</v>
+        <v>1712</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>5913</v>
+        <v>4615</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8044</v>
+        <v>9084</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2131</v>
+        <v>-4469</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7154</v>
+        <v>5998</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1453</v>
+        <v>-3086</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-10</v>
+        <v>17</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>12-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7154</v>
+        <v>5998</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>1453</v>
+        <v>-3086</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-10</v>
+        <v>17</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1971</v>
+        <v>-3086</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>14-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1971</v>
+        <v>-3086</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4948</v>
+        <v>5998</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6514</v>
+        <v>9084</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1566</v>
+        <v>-3086</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6514</v>
+        <v>9084</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1158</v>
+        <v>-3086</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1971</v>
+        <v>-3086</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4121</v>
+        <v>5998</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6514</v>
+        <v>9084</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-2393</v>
+        <v>-3086</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7154</v>
+        <v>5998</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>6514</v>
+        <v>9084</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>640</v>
+        <v>-3086</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-10</v>
+        <v>17</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>6514</v>
+        <v>9084</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1158</v>
+        <v>-3086</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>7154</v>
+        <v>7281</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1453</v>
+        <v>-1803</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>40</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>21-APR-26</t>
+          <t>03-MAY-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7672</v>
+        <v>7281</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1971</v>
+        <v>-1803</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>26-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2355,22 +2355,22 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7154</v>
+        <v>4615</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1453</v>
+        <v>-4469</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>26-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
+        <v>25</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>7672</v>
+        <v>4615</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1971</v>
+        <v>-4469</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-16</v>
+        <v>20</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>7154</v>
+        <v>5998</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1453</v>
+        <v>-3086</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-10</v>
+        <v>17</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7154</v>
+        <v>5998</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1453</v>
+        <v>-3086</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-10</v>
+        <v>17</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1971</v>
+        <v>-3086</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>05-MAY-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,33 +2666,2463 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7672</v>
+        <v>5998</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>5701</v>
+        <v>9084</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>1971</v>
+        <v>-3086</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H49" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>05-MAY-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>5998</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>05-MAY-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>5998</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>05-MAY-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>5998</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>05-MAY-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>5998</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>05-MAY-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-318</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>5998</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>05-MAY-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>5998</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-3086</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>06-MAY-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-4469</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>06-MAY-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-4469</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>06-MAY-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-4469</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>06-MAY-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-4469</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>06-MAY-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>06-MAY-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>07-MAY-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>4194</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-4890</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>07-MAY-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>4194</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-4890</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>07-MAY-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>07-MAY-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>07-MAY-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>07-MAY-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>10-MAY-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-4469</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>10-MAY-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-4469</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>10-MAY-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>10-MAY-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>9084</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-1803</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>13-MAY-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>4896</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>12059</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-7163</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>13-MAY-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>4896</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>12059</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-7163</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>10648</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-14177</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>10648</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-14177</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>12892</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-11933</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>12892</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-11933</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>15838</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-8987</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>15838</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-8987</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>15838</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-8987</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>18-MAY-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-495</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>15838</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>24825</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-8987</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>6068</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="I82" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>7281</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>6068</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-5115</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>28-MAY-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-2736</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>5737</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-3993</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>5737</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-3993</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>6719</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-3011</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>6719</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-3011</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>9245</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-485</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>31-MAY-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>9245</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-485</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,8 +60,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8327</v>
+        <v>11407</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7289</v>
+        <v>25427</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1038</v>
+        <v>-14020</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8327</v>
+        <v>13999</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7289</v>
+        <v>25427</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1038</v>
+        <v>-11428</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8327</v>
+        <v>14042</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7289</v>
+        <v>25427</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1038</v>
+        <v>-11385</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8327</v>
+        <v>16014</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7289</v>
+        <v>25427</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1038</v>
+        <v>-9413</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8565</v>
+        <v>16014</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7289</v>
+        <v>25427</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1276</v>
+        <v>-9413</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8565</v>
+        <v>16014</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7289</v>
+        <v>25427</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1276</v>
+        <v>-9413</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4615</v>
+        <v>16014</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2267</v>
+        <v>-9413</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4615</v>
+        <v>16352</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2267</v>
+        <v>-9075</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-679</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4615</v>
+        <v>16352</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2267</v>
+        <v>-9075</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>17-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4615</v>
+        <v>21495</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2267</v>
+        <v>-3932</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,40 +991,40 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-495</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7982</v>
+        <v>16014</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6882</v>
+        <v>18212</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1100</v>
+        <v>-2198</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,38 +1036,38 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-495</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7982</v>
+        <v>19748</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6882</v>
+        <v>18212</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1100</v>
+        <v>1536</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>4615</v>
+        <v>11821</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2267</v>
+        <v>-13606</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4615</v>
+        <v>15197</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2267</v>
+        <v>-10230</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>5317</v>
+        <v>16352</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1565</v>
+        <v>-9075</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>5317</v>
+        <v>20678</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6882</v>
+        <v>25427</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1565</v>
+        <v>-4749</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>20-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5317</v>
+        <v>10694</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6882</v>
+        <v>14704</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1565</v>
+        <v>-4010</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1316,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5317</v>
+        <v>17170</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6882</v>
+        <v>16254</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1565</v>
+        <v>916</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,28 +1361,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-695</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7281</v>
+        <v>17508</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>6068</v>
+        <v>16254</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1213</v>
+        <v>1254</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,28 +1406,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7281</v>
+        <v>10449</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>6068</v>
+        <v>13661</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1213</v>
+        <v>-3212</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7780</v>
+        <v>11829</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6068</v>
+        <v>13661</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1712</v>
+        <v>-1832</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>19-APR-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,28 +1496,28 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7780</v>
+        <v>11999</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6068</v>
+        <v>13661</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1712</v>
+        <v>-1662</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4615</v>
+        <v>12097</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9084</v>
+        <v>13661</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4469</v>
+        <v>-1564</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4615</v>
+        <v>12844</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>9084</v>
+        <v>13661</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4469</v>
+        <v>-817</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,28 +1631,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4615</v>
+        <v>13089</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>9084</v>
+        <v>13661</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4469</v>
+        <v>-572</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,28 +1676,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4615</v>
+        <v>13089</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>9084</v>
+        <v>13661</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4469</v>
+        <v>-572</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,28 +1721,28 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4615</v>
+        <v>7453</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4469</v>
+        <v>-4123</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>4615</v>
+        <v>11962</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4469</v>
+        <v>386</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5998</v>
+        <v>7453</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-3086</v>
+        <v>-4123</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,28 +1856,28 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5998</v>
+        <v>11962</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-3086</v>
+        <v>386</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,28 +1901,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5998</v>
+        <v>11962</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-3086</v>
+        <v>386</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,28 +1946,28 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5998</v>
+        <v>12457</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-3086</v>
+        <v>881</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,28 +1991,28 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5998</v>
+        <v>11962</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-3086</v>
+        <v>386</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,28 +2036,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5998</v>
+        <v>11962</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-3086</v>
+        <v>386</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5998</v>
+        <v>7453</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-3086</v>
+        <v>-4123</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5998</v>
+        <v>11962</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3086</v>
+        <v>386</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5998</v>
+        <v>6749</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-3086</v>
+        <v>-4827</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5998</v>
+        <v>6749</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-3086</v>
+        <v>-4827</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2490,24 +2490,24 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4615</v>
+        <v>8862</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-4469</v>
+        <v>-2714</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5998</v>
+        <v>6044</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-3086</v>
+        <v>-5532</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5998</v>
+        <v>6749</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-3086</v>
+        <v>-4827</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5998</v>
+        <v>7011</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-3086</v>
+        <v>-4565</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>23</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2670,26 +2670,26 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5998</v>
+        <v>7011</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-3086</v>
+        <v>-4565</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>23</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2715,26 +2715,26 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5998</v>
+        <v>7011</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-3086</v>
+        <v>-4565</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2760,26 +2760,26 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5998</v>
+        <v>7011</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-3086</v>
+        <v>-4565</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>23</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2805,26 +2805,26 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5998</v>
+        <v>7011</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-3086</v>
+        <v>-4565</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>23</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,28 +2846,28 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5998</v>
+        <v>8862</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-3086</v>
+        <v>-2714</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,28 +2891,28 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5998</v>
+        <v>13113</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-3086</v>
+        <v>1537</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,28 +2936,28 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>5998</v>
+        <v>6749</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-3086</v>
+        <v>-4827</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,28 +2981,28 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4615</v>
+        <v>6749</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-4469</v>
+        <v>-4827</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>15</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,30 +3071,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4615</v>
+        <v>7011</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-4469</v>
+        <v>-4565</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,30 +3161,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7281</v>
+        <v>7011</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1803</v>
+        <v>-4565</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>7</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,28 +3206,28 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>7281</v>
+        <v>8862</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1803</v>
+        <v>-2714</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>07-MAY-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,1878 +3251,33 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>4194</v>
+        <v>8862</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>9084</v>
+        <v>11576</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-4890</v>
+        <v>-2714</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>07-MAY-26</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>4194</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>-4890</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>07-MAY-26</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>-4469</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>07-MAY-26</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>-4469</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>07-MAY-26</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>-4469</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>07-MAY-26</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>-4469</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>10-MAY-26</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>-4469</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>10-MAY-26</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>-4469</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>10-MAY-26</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>7281</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>-1803</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>10-MAY-26</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>7281</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>9084</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>-1803</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>13-MAY-26</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>4896</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>12059</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>-7163</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>13-MAY-26</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>4896</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>12059</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>-7163</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>10648</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>-14177</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>10648</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>-14177</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>12892</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>-11933</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>12892</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>-11933</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>13173</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>-11652</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>13173</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>-11652</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>13173</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>-11652</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>18-MAY-26</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>SM-495</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>13173</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>24825</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>-11652</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>27-MAY-26</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>7281</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>6068</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>27-MAY-26</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>7281</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>6068</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>-5115</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>-5115</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>-5115</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>-5115</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>-5115</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>4615</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>-5115</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-314</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-316</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-314</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-316</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>6994</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>-2736</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>5737</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>-3993</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>5737</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>-3993</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>7421</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>-2309</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>7421</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>-2309</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>9245</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>-485</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>9245</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>9730</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>-485</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,40 +541,40 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-495</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>11407</v>
+        <v>16014</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>25427</v>
+        <v>18212</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-14020</v>
+        <v>-2198</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,40 +586,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-495</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-4058</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>13999</v>
+        <v>17170</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>25427</v>
+        <v>18212</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-11428</v>
+        <v>-1042</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>18-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-493</t>
+          <t>SM-495</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>14042</v>
+        <v>17508</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25427</v>
+        <v>18212</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-11385</v>
+        <v>-704</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,28 +686,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>16014</v>
+        <v>10694</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>25427</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-9413</v>
+        <v>-14733</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>16014</v>
+        <v>14042</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>25427</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-9413</v>
+        <v>-11385</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>16014</v>
+        <v>15197</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>25427</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-9413</v>
+        <v>-10230</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>16014</v>
+        <v>17170</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>25427</v>
+        <v>16254</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-9413</v>
+        <v>916</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>16352</v>
+        <v>11829</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>25427</v>
+        <v>13661</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-9075</v>
+        <v>-1832</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-679</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16352</v>
+        <v>12097</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>25427</v>
+        <v>13661</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-9075</v>
+        <v>-1564</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>21495</v>
+        <v>12097</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25427</v>
+        <v>13661</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3932</v>
+        <v>-1564</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,27 +991,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16014</v>
+        <v>12844</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18212</v>
+        <v>13661</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2198</v>
+        <v>-817</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,7 +1022,7 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1036,36 +1036,36 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>19748</v>
+        <v>13089</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18212</v>
+        <v>13661</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1536</v>
+        <v>-572</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11821</v>
+        <v>13089</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25427</v>
+        <v>13661</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-13606</v>
+        <v>-572</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>15197</v>
+        <v>14859</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>25427</v>
+        <v>13661</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-10230</v>
+        <v>1198</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16352</v>
+        <v>7453</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>25427</v>
+        <v>11576</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-9075</v>
+        <v>-4123</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>20678</v>
+        <v>11962</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>25427</v>
+        <v>11576</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4749</v>
+        <v>386</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10694</v>
+        <v>7453</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14704</v>
+        <v>11576</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4010</v>
+        <v>-4123</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>17170</v>
+        <v>11962</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16254</v>
+        <v>11576</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>916</v>
+        <v>386</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-695</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>17508</v>
+        <v>11962</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16254</v>
+        <v>11576</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1254</v>
+        <v>386</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10449</v>
+        <v>11962</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-3212</v>
+        <v>386</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11829</v>
+        <v>11962</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1832</v>
+        <v>386</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11999</v>
+        <v>12457</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1662</v>
+        <v>881</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>12097</v>
+        <v>11962</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1564</v>
+        <v>386</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>12844</v>
+        <v>11962</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-817</v>
+        <v>386</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>13089</v>
+        <v>11962</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-572</v>
+        <v>386</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>13089</v>
+        <v>7453</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>13661</v>
+        <v>11576</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-572</v>
+        <v>-4123</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,22 +1725,22 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7453</v>
+        <v>11962</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4123</v>
+        <v>386</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>11962</v>
+        <v>6044</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>386</v>
+        <v>-5532</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,22 +1815,22 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7453</v>
+        <v>11962</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-4123</v>
+        <v>386</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,22 +1860,22 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>11962</v>
+        <v>6749</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>386</v>
+        <v>-4827</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1905,22 +1905,22 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>11962</v>
+        <v>6749</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>386</v>
+        <v>-4827</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>12457</v>
+        <v>7011</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>881</v>
+        <v>-4565</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>11962</v>
+        <v>7011</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>386</v>
+        <v>-4565</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>23-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>11962</v>
+        <v>7011</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>386</v>
+        <v>-4565</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7453</v>
+        <v>7011</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4123</v>
+        <v>-4565</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>11962</v>
+        <v>7011</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>386</v>
+        <v>-4565</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6749</v>
+        <v>8862</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-4827</v>
+        <v>-2714</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>6749</v>
+        <v>7011</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-4827</v>
+        <v>-4565</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2282,7 +2282,7 @@
       <c r="I40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2327,7 +2327,7 @@
       <c r="I41" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2372,7 +2372,7 @@
       <c r="I42" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2417,7 +2417,7 @@
       <c r="I43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7011</v>
+        <v>9716</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-4565</v>
+        <v>-1860</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>23</v>
@@ -2462,9 +2462,9 @@
       <c r="I44" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>8862</v>
+        <v>6749</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-2714</v>
+        <v>-4827</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>6044</v>
+        <v>6749</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-5532</v>
+        <v>-4827</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>15</v>
@@ -2552,9 +2552,9 @@
       <c r="I46" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6749</v>
+        <v>7011</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-4827</v>
+        <v>-4565</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2687,7 +2687,7 @@
       <c r="I49" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -2732,7 +2732,7 @@
       <c r="I50" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>7011</v>
+        <v>8862</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-4565</v>
+        <v>-2714</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,483 +2801,33 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>7011</v>
+        <v>8862</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>11576</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-4565</v>
+        <v>-2714</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>8862</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>-2714</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-4058</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>13113</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>1537</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>6749</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>-4827</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>6749</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>-4827</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-314</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-316</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>8862</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>-2714</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>8862</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>-2714</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16014</v>
+        <v>16993</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18212</v>
+        <v>18025</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2198</v>
+        <v>-1032</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17170</v>
+        <v>17328</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18212</v>
+        <v>18025</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1042</v>
+        <v>-697</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -631,40 +631,40 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>17508</v>
+        <v>9747</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18212</v>
+        <v>25165</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-704</v>
+        <v>-15418</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10694</v>
+        <v>13897</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25427</v>
+        <v>25165</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-14733</v>
+        <v>-11268</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14042</v>
+        <v>15041</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25427</v>
+        <v>25165</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-11385</v>
+        <v>-10124</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15197</v>
+        <v>9747</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>25427</v>
+        <v>16087</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-10230</v>
+        <v>-6340</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>EgyptAir MS-675</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17170</v>
+        <v>13897</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16254</v>
+        <v>16087</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>916</v>
+        <v>-2190</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>EgyptAir MS-693</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11829</v>
+        <v>15041</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13661</v>
+        <v>16087</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1832</v>
+        <v>-1046</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12097</v>
+        <v>16993</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13661</v>
+        <v>16087</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1564</v>
+        <v>906</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12097</v>
+        <v>11708</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13661</v>
+        <v>13521</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1564</v>
+        <v>-1813</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>23</v>
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12844</v>
+        <v>11973</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13661</v>
+        <v>13521</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-817</v>
+        <v>-1548</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13089</v>
+        <v>11973</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13661</v>
+        <v>13521</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-572</v>
+        <v>-1548</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>EgyptAir MS-677</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13089</v>
+        <v>12712</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13661</v>
+        <v>13521</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-572</v>
+        <v>-809</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14859</v>
+        <v>12955</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13661</v>
+        <v>13521</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1198</v>
+        <v>-566</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7453</v>
+        <v>12955</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11576</v>
+        <v>13521</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4123</v>
+        <v>-566</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>EgyptAir MS-639</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>11962</v>
+        <v>14706</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11576</v>
+        <v>13521</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>386</v>
+        <v>1185</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7453</v>
+        <v>7377</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4123</v>
+        <v>-4080</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15</v>
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>11962</v>
+        <v>11839</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>40</v>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11962</v>
+        <v>11839</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>40</v>
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11962</v>
+        <v>11839</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>40</v>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11962</v>
+        <v>11839</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>40</v>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>12457</v>
+        <v>11839</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>881</v>
+        <v>382</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>40</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>11962</v>
+        <v>11839</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>40</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>23-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>11962</v>
+        <v>11839</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>40</v>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>11962</v>
+        <v>7377</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>386</v>
+        <v>-4080</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7453</v>
+        <v>11839</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4123</v>
+        <v>382</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,22 +1725,22 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>11962</v>
+        <v>6679</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>386</v>
+        <v>-4778</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6044</v>
+        <v>6679</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-5532</v>
+        <v>-4778</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>15</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>11962</v>
+        <v>6938</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>386</v>
+        <v>-4519</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6749</v>
+        <v>6938</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-4827</v>
+        <v>-4519</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6749</v>
+        <v>6938</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-4827</v>
+        <v>-4519</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>23</v>
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>23</v>
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7011</v>
+        <v>8771</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-4565</v>
+        <v>-2686</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>23</v>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>23</v>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8862</v>
+        <v>6938</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-2714</v>
+        <v>-4519</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>23</v>
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>23</v>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7011</v>
+        <v>9616</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-4565</v>
+        <v>-1841</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>23</v>
@@ -2327,9 +2327,9 @@
       <c r="I41" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>23</v>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7011</v>
+        <v>6938</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-4565</v>
+        <v>-4519</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>23</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-4058</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>9716</v>
+        <v>6938</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1860</v>
+        <v>-4519</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>23</v>
@@ -2462,9 +2462,9 @@
       <c r="I44" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2486,348 +2486,33 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6749</v>
+        <v>6938</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11576</v>
+        <v>11457</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-4827</v>
+        <v>-4519</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>6749</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>-4827</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-314</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-316</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>-4565</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>8862</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>-2714</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>8862</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>11576</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>-2714</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,20 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,40 +532,40 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>16993</v>
+        <v>7377</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18025</v>
+        <v>11443</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1032</v>
+        <v>-4066</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,40 +577,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>18-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-495</t>
+          <t>SM-493</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17328</v>
+        <v>7377</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>18025</v>
+        <v>11415</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-697</v>
+        <v>-4038</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,26 +636,26 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9747</v>
+        <v>11839</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25165</v>
+        <v>11443</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-15418</v>
+        <v>396</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13897</v>
+        <v>11839</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25165</v>
+        <v>11415</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-11268</v>
+        <v>424</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>15041</v>
+        <v>11839</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>25165</v>
+        <v>11443</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-10124</v>
+        <v>396</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -780,26 +771,26 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9747</v>
+        <v>11839</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16087</v>
+        <v>11415</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6340</v>
+        <v>424</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +812,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-675</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13897</v>
+        <v>11839</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16087</v>
+        <v>11443</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2190</v>
+        <v>396</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-693</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>15041</v>
+        <v>11839</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16087</v>
+        <v>11415</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1046</v>
+        <v>424</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>30-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16993</v>
+        <v>11839</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16087</v>
+        <v>11443</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>906</v>
+        <v>396</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>30-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11708</v>
+        <v>11839</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13521</v>
+        <v>11415</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1813</v>
+        <v>424</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11973</v>
+        <v>7377</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13521</v>
+        <v>11443</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1548</v>
+        <v>-4066</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11973</v>
+        <v>7377</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13521</v>
+        <v>11415</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1548</v>
+        <v>-4038</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-677</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12712</v>
+        <v>11839</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13521</v>
+        <v>11443</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-809</v>
+        <v>396</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12955</v>
+        <v>11839</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13521</v>
+        <v>11415</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-566</v>
+        <v>424</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1172,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12955</v>
+        <v>5982</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13521</v>
+        <v>11443</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-566</v>
+        <v>-5461</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1217,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-639</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14706</v>
+        <v>5982</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>13521</v>
+        <v>11415</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1185</v>
+        <v>-5433</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,26 +1266,26 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7377</v>
+        <v>11839</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4080</v>
+        <v>396</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1307,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
         <v>11839</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>40</v>
@@ -1337,9 +1328,9 @@
       <c r="I19" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11839</v>
+        <v>6679</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>382</v>
+        <v>-4764</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1397,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11839</v>
+        <v>6679</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>382</v>
+        <v>-4764</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,26 +1446,26 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11839</v>
+        <v>6679</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>382</v>
+        <v>-4736</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1487,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11839</v>
+        <v>6679</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>382</v>
+        <v>-4736</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>23-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1532,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>11839</v>
+        <v>6994</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>382</v>
+        <v>-4449</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1577,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>11839</v>
+        <v>6994</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>382</v>
+        <v>-4449</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1622,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7377</v>
+        <v>6994</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4080</v>
+        <v>-4449</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1667,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>11839</v>
+        <v>6994</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>382</v>
+        <v>-4449</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1721,30 +1712,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6679</v>
+        <v>6994</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4778</v>
+        <v>-4449</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1766,30 +1757,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6679</v>
+        <v>6994</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4778</v>
+        <v>-4421</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1811,17 +1802,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>23</v>
@@ -1832,9 +1823,9 @@
       <c r="I30" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1856,17 +1847,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>23</v>
@@ -1877,9 +1868,9 @@
       <c r="I31" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1901,17 +1892,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>23</v>
@@ -1922,9 +1913,9 @@
       <c r="I32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1946,17 +1937,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>23</v>
@@ -1967,9 +1958,9 @@
       <c r="I33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1991,30 +1982,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>6938</v>
+        <v>8771</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-4519</v>
+        <v>-2672</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2043,10 +2034,10 @@
         <v>8771</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-2686</v>
+        <v>-2644</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2057,9 +2048,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2085,13 +2076,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4519</v>
+        <v>-4449</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>23</v>
@@ -2102,9 +2093,9 @@
       <c r="I36" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2130,13 +2121,13 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-4519</v>
+        <v>-4449</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>23</v>
@@ -2147,9 +2138,9 @@
       <c r="I37" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2175,13 +2166,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-4519</v>
+        <v>-4449</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>23</v>
@@ -2192,9 +2183,9 @@
       <c r="I38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2220,13 +2211,13 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-4519</v>
+        <v>-4449</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>23</v>
@@ -2237,9 +2228,9 @@
       <c r="I39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2265,13 +2256,13 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11457</v>
+        <v>11443</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4519</v>
+        <v>-4449</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>23</v>
@@ -2282,9 +2273,9 @@
       <c r="I40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2306,17 +2297,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-4058</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9616</v>
+        <v>6994</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1841</v>
+        <v>-4421</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>23</v>
@@ -2327,9 +2318,9 @@
       <c r="I41" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2332,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2342,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>23</v>
@@ -2372,9 +2363,9 @@
       <c r="I42" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2377,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2400,13 +2391,13 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>23</v>
@@ -2417,9 +2408,9 @@
       <c r="I43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2422,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2445,13 +2436,13 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>23</v>
@@ -2462,9 +2453,9 @@
       <c r="I44" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2467,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2490,13 +2481,13 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6938</v>
+        <v>6994</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11457</v>
+        <v>11415</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-4519</v>
+        <v>-4421</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>23</v>
@@ -2507,12 +2498,822 @@
       <c r="I45" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-4058</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>9825</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-1618</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-4058</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>9825</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1590</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>6679</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-4764</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>6679</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-4764</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>6679</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-4736</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>6679</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-4736</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-4449</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-4449</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-4449</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-4449</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-4421</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-4421</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-4421</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>6994</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-4421</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>8771</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-2672</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>8771</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>11443</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-2672</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>8771</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-2644</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>8771</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>11415</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-2644</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7771</v>
+        <v>7736</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7864</v>
+        <v>11578</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-93</v>
+        <v>-3842</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,33 +587,1293 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>09-AUG-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>09-AUG-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>19-AUG-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>26-AUG-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06-SEP-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6327</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-5251</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>06-SEP-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>12246</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>668</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7032</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-4546</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>7032</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-4546</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-318</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>flynas XY-575</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>7771</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>7864</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-93</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="D17" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-318</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-4058</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9929</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-1649</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>7032</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-4546</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>7032</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-4546</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>8548</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-3030</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7736</v>
+        <v>9005</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11578</v>
+        <v>7829</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3842</v>
+        <v>1176</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12246</v>
+        <v>7736</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>668</v>
+        <v>-3842</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,22 +681,22 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12246</v>
+        <v>8441</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>668</v>
+        <v>-3137</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,26 +816,26 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6327</v>
+        <v>12740</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5251</v>
+        <v>1162</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7032</v>
+        <v>12246</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4546</v>
+        <v>668</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7032</v>
+        <v>12740</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11578</v>
+        <v>12621</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4546</v>
+        <v>119</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7068</v>
+        <v>12246</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4510</v>
+        <v>668</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>30-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7068</v>
+        <v>12740</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4510</v>
+        <v>1162</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7068</v>
+        <v>8441</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4510</v>
+        <v>-3137</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7068</v>
+        <v>12246</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4510</v>
+        <v>668</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1172,30 +1172,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7068</v>
+        <v>7032</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4510</v>
+        <v>-4546</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7454</v>
+        <v>7032</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4124</v>
+        <v>-4546</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>15</v>
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,30 +1487,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-4058</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9929</v>
+        <v>10132</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1649</v>
+        <v>-1446</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7032</v>
+        <v>6327</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4546</v>
+        <v>-5251</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>15</v>
@@ -1553,9 +1553,9 @@
       <c r="I24" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,30 +1757,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7454</v>
+        <v>7068</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4124</v>
+        <v>-4510</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,30 +1802,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7454</v>
+        <v>7068</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-4124</v>
+        <v>-4510</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1837,43 +1837,448 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-4058</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>9929</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1649</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>10-SEP-26</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7032</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-4546</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7032</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-4546</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-4510</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Saudia SV-316</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D40" s="2" t="n">
         <v>8548</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F31" s="2" t="n">
+      <c r="E40" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F40" s="2" t="n">
         <v>-3030</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12740</v>
+        <v>12246</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1162</v>
+        <v>668</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>40</v>
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12246</v>
+        <v>12740</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>668</v>
+        <v>1162</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>40</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>23-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12740</v>
+        <v>12246</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12621</v>
+        <v>11578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>119</v>
+        <v>668</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>40</v>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>23-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12246</v>
+        <v>12740</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11578</v>
+        <v>12621</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>668</v>
+        <v>119</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>40</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>30-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12740</v>
+        <v>12246</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1162</v>
+        <v>668</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>40</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>30-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8441</v>
+        <v>12740</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3137</v>
+        <v>1162</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1127,26 +1127,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12246</v>
+        <v>8441</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>668</v>
+        <v>-3137</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7032</v>
+        <v>12246</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4546</v>
+        <v>668</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7032</v>
+        <v>6327</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4546</v>
+        <v>-5251</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>15</v>
@@ -1238,9 +1238,9 @@
       <c r="I17" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7068</v>
+        <v>12246</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4510</v>
+        <v>668</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1307,30 +1307,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7068</v>
+        <v>7032</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4510</v>
+        <v>-4546</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7068</v>
+        <v>7032</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4510</v>
+        <v>-4546</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1487,26 +1487,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10132</v>
+        <v>7068</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1446</v>
+        <v>-4510</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,26 +1532,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6327</v>
+        <v>7068</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-5251</v>
+        <v>-4510</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,30 +1577,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7032</v>
+        <v>7068</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4546</v>
+        <v>-4510</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,30 +1622,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7068</v>
+        <v>7454</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4510</v>
+        <v>-4124</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1667,26 +1667,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7068</v>
+        <v>6327</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4510</v>
+        <v>-5251</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1712,30 +1712,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7068</v>
+        <v>7032</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4510</v>
+        <v>-4546</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1847,30 +1847,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7454</v>
+        <v>7068</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-4124</v>
+        <v>-4510</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-4058</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>9929</v>
+        <v>7068</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1649</v>
+        <v>-4510</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>23</v>
@@ -1913,9 +1913,9 @@
       <c r="I32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,30 +1937,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7032</v>
+        <v>7068</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4546</v>
+        <v>-4510</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7032</v>
+        <v>7454</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-4546</v>
+        <v>-4124</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>15</v>
@@ -2017,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7068</v>
+        <v>9929</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-4510</v>
+        <v>-1649</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>23</v>
@@ -2048,9 +2048,9 @@
       <c r="I35" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2072,30 +2072,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7068</v>
+        <v>7032</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4510</v>
+        <v>-4546</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2117,30 +2117,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7068</v>
+        <v>7032</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-4510</v>
+        <v>-4546</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2162,30 +2162,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>7454</v>
+        <v>7068</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-4124</v>
+        <v>-4510</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2207,30 +2207,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7454</v>
+        <v>7068</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-4124</v>
+        <v>-4510</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8548</v>
+        <v>7068</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-3030</v>
+        <v>-4510</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>23</v>
@@ -2273,12 +2273,147 @@
       <c r="I40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>7454</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-4124</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>8548</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-3030</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>10132</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>11578</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1446</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12740</v>
+        <v>12246</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1162</v>
+        <v>668</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>40</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,26 +992,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12740</v>
+        <v>8441</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12621</v>
+        <v>11578</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>119</v>
+        <v>-3137</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>30-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,26 +1086,26 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12740</v>
+        <v>6327</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1162</v>
+        <v>-5251</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8441</v>
+        <v>12246</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3137</v>
+        <v>668</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1172,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12246</v>
+        <v>7068</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>668</v>
+        <v>-4510</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,26 +1217,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6327</v>
+        <v>7068</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5251</v>
+        <v>-4510</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12246</v>
+        <v>7068</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>668</v>
+        <v>-4510</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1307,30 +1307,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7032</v>
+        <v>7068</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4546</v>
+        <v>-4510</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7032</v>
+        <v>7068</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4546</v>
+        <v>-4510</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,26 +1622,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7454</v>
+        <v>9929</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4124</v>
+        <v>-1649</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6327</v>
+        <v>7032</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-5251</v>
+        <v>-4546</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>15</v>
@@ -1688,9 +1688,9 @@
       <c r="I27" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1837,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,30 +1892,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7068</v>
+        <v>7454</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-4510</v>
+        <v>-4124</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,30 +1937,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7068</v>
+        <v>7454</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4510</v>
+        <v>-4124</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,26 +1982,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7454</v>
+        <v>8548</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>11578</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-4124</v>
+        <v>-3030</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2009,411 +2009,6 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-4058</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>9929</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-1649</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>7032</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>-4546</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>7032</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>-4546</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-314</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>7068</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>-4510</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>7068</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>-4510</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>7068</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>-4510</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>7454</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>-4124</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-316</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>8548</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>-3030</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>10132</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>11578</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>-1446</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9005</v>
+        <v>7016</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7829</v>
+        <v>10255</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1176</v>
+        <v>-3239</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7736</v>
+        <v>7016</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11578</v>
+        <v>10255</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3842</v>
+        <v>-3239</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11578</v>
+        <v>10255</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>668</v>
+        <v>-3239</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8441</v>
+        <v>7016</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11578</v>
+        <v>10255</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3137</v>
+        <v>-3239</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11578</v>
+        <v>10255</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>668</v>
+        <v>-3239</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11578</v>
+        <v>8943</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>668</v>
+        <v>-1927</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11578</v>
+        <v>8943</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>668</v>
+        <v>-1927</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,26 +857,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11578</v>
+        <v>8943</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>668</v>
+        <v>-1927</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +902,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11578</v>
+        <v>8943</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>668</v>
+        <v>-1927</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12246</v>
+        <v>7016</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11578</v>
+        <v>8943</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>668</v>
+        <v>-1927</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8441</v>
+        <v>7664</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3137</v>
+        <v>-3890</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>15</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12246</v>
+        <v>12132</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>668</v>
+        <v>578</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>40</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6327</v>
+        <v>8362</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5251</v>
+        <v>-3192</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>15</v>
@@ -1103,9 +1103,9 @@
       <c r="I14" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06-SEP-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12246</v>
+        <v>12132</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>668</v>
+        <v>578</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>40</v>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1172,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7068</v>
+        <v>12132</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4510</v>
+        <v>578</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,30 +1217,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7068</v>
+        <v>12622</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4510</v>
+        <v>1068</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7068</v>
+        <v>12132</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4510</v>
+        <v>578</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,30 +1307,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7068</v>
+        <v>12132</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4510</v>
+        <v>578</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>30-AUG-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7068</v>
+        <v>12622</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4510</v>
+        <v>1068</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,30 +1397,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>7068</v>
+        <v>8362</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4510</v>
+        <v>-3192</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,30 +1442,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7068</v>
+        <v>12132</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4510</v>
+        <v>578</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,30 +1487,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7068</v>
+        <v>6966</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-4510</v>
+        <v>-4588</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,30 +1532,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7068</v>
+        <v>6966</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4510</v>
+        <v>-4588</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7068</v>
+        <v>7016</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4510</v>
+        <v>-4538</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>23</v>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-4058</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9929</v>
+        <v>7016</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-1649</v>
+        <v>-4538</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>23</v>
@@ -1643,9 +1643,9 @@
       <c r="I26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,30 +1667,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7032</v>
+        <v>7016</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4546</v>
+        <v>-4538</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7032</v>
+        <v>7385</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4546</v>
+        <v>-4169</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>15</v>
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7068</v>
+        <v>8482</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4510</v>
+        <v>-3072</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>23</v>
@@ -1778,9 +1778,9 @@
       <c r="I29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7068</v>
+        <v>8482</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-4510</v>
+        <v>-3072</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>23</v>
@@ -1823,9 +1823,9 @@
       <c r="I30" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1847,30 +1847,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7068</v>
+        <v>6966</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-4510</v>
+        <v>-4588</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-794</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7454</v>
+        <v>6966</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-4124</v>
+        <v>-4588</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>15</v>
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,30 +1937,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>Saudia SV-314</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7454</v>
+        <v>7016</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4124</v>
+        <v>-4538</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,17 +1982,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8548</v>
+        <v>7016</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11578</v>
+        <v>11554</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-3030</v>
+        <v>-4538</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>23</v>
@@ -2003,12 +2003,552 @@
       <c r="I34" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>7016</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-4538</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>7016</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-4538</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7016</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-4538</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>7385</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-4169</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-776</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>6966</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-4588</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-772</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>6966</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-4588</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-314</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>7016</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-4538</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-390</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>7016</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-4538</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-794</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>7385</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-4169</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-575</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>7385</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-4169</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-316</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>8482</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-493</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-380</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>8482</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>11554</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-3072</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_MED_threats.xlsx
+++ b/excel_routes/route_CAI_MED_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7016</v>
+        <v>6880</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10255</v>
+        <v>9502</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3239</v>
+        <v>-2622</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>23</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7016</v>
+        <v>6880</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10255</v>
+        <v>9502</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3239</v>
+        <v>-2622</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>23</v>
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>Saudia SV-316</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7016</v>
+        <v>6880</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10255</v>
+        <v>9502</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3239</v>
+        <v>-2622</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>23</v>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7016</v>
+        <v>8818</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10255</v>
+        <v>9502</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3239</v>
+        <v>-684</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7016</v>
+        <v>8266</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10255</v>
+        <v>11448</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3239</v>
+        <v>-3182</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>02-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7016</v>
+        <v>11992</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8943</v>
+        <v>11448</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1927</v>
+        <v>544</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7016</v>
+        <v>9094</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8943</v>
+        <v>11448</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1927</v>
+        <v>-2354</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,26 +857,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7016</v>
+        <v>11992</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8943</v>
+        <v>11448</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1927</v>
+        <v>544</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>09-AUG-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +902,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7016</v>
+        <v>11992</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8943</v>
+        <v>11448</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1927</v>
+        <v>544</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7016</v>
+        <v>11992</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8943</v>
+        <v>11448</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-1927</v>
+        <v>544</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -996,22 +996,22 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7664</v>
+        <v>11992</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3890</v>
+        <v>544</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>02-AUG-26</t>
+          <t>26-AUG-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12132</v>
+        <v>11992</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>40</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>30-AUG-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8362</v>
+        <v>12476</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3192</v>
+        <v>1028</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1127,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12132</v>
+        <v>8266</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>578</v>
+        <v>-3182</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12132</v>
+        <v>11992</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>40</v>
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1221,26 +1221,26 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>12622</v>
+        <v>6196</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1068</v>
+        <v>-5252</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>06-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12132</v>
+        <v>11992</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>40</v>
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>26-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,30 +1307,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>12132</v>
+        <v>6880</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>578</v>
+        <v>-4568</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>30-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>12622</v>
+        <v>6880</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1068</v>
+        <v>-4568</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8362</v>
+        <v>6886</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-3192</v>
+        <v>-4562</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>15</v>
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,26 +1442,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>12132</v>
+        <v>6886</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>578</v>
+        <v>-4562</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1487,26 +1487,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6966</v>
+        <v>8481</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-4588</v>
+        <v>-2967</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1532,30 +1532,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6966</v>
+        <v>9922</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4588</v>
+        <v>-1526</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,26 +1577,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7016</v>
+        <v>6196</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4538</v>
+        <v>-5252</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-318</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7016</v>
+        <v>6880</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4538</v>
+        <v>-4568</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>23</v>
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7016</v>
+        <v>6880</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4538</v>
+        <v>-4568</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>23</v>
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-575</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7385</v>
+        <v>6886</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4169</v>
+        <v>-4562</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>15</v>
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,26 +1757,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>8482</v>
+        <v>7300</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-3072</v>
+        <v>-4148</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8482</v>
+        <v>8233</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-3072</v>
+        <v>-3215</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>23</v>
@@ -1847,26 +1847,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-776</t>
+          <t>Saudia SV-4058</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>6966</v>
+        <v>9530</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-4588</v>
+        <v>-1918</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,30 +1892,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-772</t>
+          <t>Saudia SV-390</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>6966</v>
+        <v>6880</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-4588</v>
+        <v>-4568</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,30 +1937,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-314</t>
+          <t>flyadeal F3-776</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7016</v>
+        <v>6886</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-4538</v>
+        <v>-4562</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,30 +1982,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-318</t>
+          <t>flyadeal F3-772</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7016</v>
+        <v>6886</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-4538</v>
+        <v>-4562</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-316</t>
+          <t>Saudia SV-380</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>7016</v>
+        <v>8233</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-4538</v>
+        <v>-3215</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>23</v>
@@ -2048,9 +2048,9 @@
       <c r="I35" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2072,26 +2072,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-390</t>
+          <t>flynas XY-794</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7016</v>
+        <v>9922</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4538</v>
+        <v>-1526</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2117,26 +2117,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-380</t>
+          <t>flynas XY-575</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7016</v>
+        <v>9922</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11554</v>
+        <v>11448</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-4538</v>
+        <v>-1526</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2144,411 +2144,6 @@
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>7385</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>-4169</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-776</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>6966</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>-4588</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-772</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>6966</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>-4588</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-314</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>7016</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>-4538</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-390</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>7016</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>-4538</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-794</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>7385</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>-4169</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-575</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>7385</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>-4169</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-316</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>8482</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>-3072</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>10-SEP-26</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SM-493</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-380</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>8482</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>11554</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>-3072</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
